--- a/Luban/Excel/角色战斗主表.xlsx
+++ b/Luban/Excel/角色战斗主表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="239">
   <si>
     <t>主键</t>
   </si>
@@ -64,6 +64,12 @@
     <t>术杀式</t>
   </si>
   <si>
+    <t>额外招式数量</t>
+  </si>
+  <si>
+    <t>额外招式</t>
+  </si>
+  <si>
     <t>战斗台词组</t>
   </si>
   <si>
@@ -118,6 +124,9 @@
     <t>#术杀式</t>
   </si>
   <si>
+    <t>#额外招式</t>
+  </si>
+  <si>
     <t>#备注</t>
   </si>
   <si>
@@ -394,22 +403,46 @@
     <t>渔人</t>
   </si>
   <si>
-    <t>杀机无相</t>
-  </si>
-  <si>
-    <t>11030|11032</t>
-  </si>
-  <si>
-    <t>遁江|堵截</t>
-  </si>
-  <si>
-    <t>13022|13061|13062</t>
-  </si>
-  <si>
-    <t>掠捕|破镜|大鱼上钩</t>
-  </si>
-  <si>
-    <t>气定神闲</t>
+    <t>10116|10152</t>
+  </si>
+  <si>
+    <t>杀机无相|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11005</t>
+  </si>
+  <si>
+    <t>遁江|招架</t>
+  </si>
+  <si>
+    <t>13022|13061|13067|13053</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|沉舟擒钩|夺梢</t>
+  </si>
+  <si>
+    <t>屏息凝神</t>
+  </si>
+  <si>
+    <t>邵民瑞一方渔人</t>
+  </si>
+  <si>
+    <t>13022|13061|13067|13007</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|沉舟擒钩|迅攻</t>
+  </si>
+  <si>
+    <t>11030|11005|11029</t>
+  </si>
+  <si>
+    <t>遁江|招架|周旋</t>
+  </si>
+  <si>
+    <t>13022|13061|13067</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|沉舟擒钩</t>
   </si>
   <si>
     <t>迷精</t>
@@ -511,7 +544,208 @@
     <t>诺融伤</t>
   </si>
   <si>
+    <t>10092|10045|10154|10153</t>
+  </si>
+  <si>
+    <t>捕醉仙|清梦醉眀|酒痴|梦为自如真</t>
+  </si>
+  <si>
+    <t>14085|14086</t>
+  </si>
+  <si>
+    <t>熏饮西风|迎酌北风</t>
+  </si>
+  <si>
     <t>猖诞教教徒</t>
+  </si>
+  <si>
+    <t>10109|10151|10152</t>
+  </si>
+  <si>
+    <t>毅定风波|昂膀|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11032|11009</t>
+  </si>
+  <si>
+    <t>遁江|围追堵截|聚炁</t>
+  </si>
+  <si>
+    <t>13022|13061|13068|13001</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|天罗地网|佯攻</t>
+  </si>
+  <si>
+    <t>13022|13061|13068|13004</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|天罗地网|试探试探</t>
+  </si>
+  <si>
+    <t>11030|11032|11009|11005</t>
+  </si>
+  <si>
+    <t>遁江|围追堵截|聚炁|招架</t>
+  </si>
+  <si>
+    <t>13022|13061|13068|13071</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|天罗地网|断潮索</t>
+  </si>
+  <si>
+    <t>邵民瑞</t>
+  </si>
+  <si>
+    <t>10116|10131|10001|10016|10152</t>
+  </si>
+  <si>
+    <t>杀机无相|抢占先机|武师职能|无往蹈锋|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11009|11029</t>
+  </si>
+  <si>
+    <t>遁江|聚炁|周旋</t>
+  </si>
+  <si>
+    <t>13022|13062|13067|13070</t>
+  </si>
+  <si>
+    <t>掠捕|大鱼上钩|沉舟擒钩|黑舸翻波</t>
+  </si>
+  <si>
+    <t>滕老湍</t>
+  </si>
+  <si>
+    <t>10109|10151|10003|10016|10152</t>
+  </si>
+  <si>
+    <t>毅定风波|昂膀|铁卫职能|无往蹈锋|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11009|11005</t>
+  </si>
+  <si>
+    <t>遁江|聚炁|招架</t>
+  </si>
+  <si>
+    <t>13022|13062|13068|13069</t>
+  </si>
+  <si>
+    <t>掠捕|大鱼上钩|天罗地网|断潮索</t>
+  </si>
+  <si>
+    <t>江槎</t>
+  </si>
+  <si>
+    <t>10109|10118|10151|10016|10152</t>
+  </si>
+  <si>
+    <t>毅定风波|水骨不折|昂膀|无往蹈锋|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11032|11009|11053</t>
+  </si>
+  <si>
+    <t>遁江|围追堵截|聚炁|水戈再起</t>
+  </si>
+  <si>
+    <t>13022|13061|13068|13069</t>
+  </si>
+  <si>
+    <t>鲛九</t>
+  </si>
+  <si>
+    <t>10117|10016|10152</t>
+  </si>
+  <si>
+    <t>杀机无相|无往蹈锋|水生之道</t>
+  </si>
+  <si>
+    <t>11030|11029</t>
+  </si>
+  <si>
+    <t>遁江|周旋</t>
+  </si>
+  <si>
+    <t>13022|13061|13067|13070</t>
+  </si>
+  <si>
+    <t>掠捕|破镜|沉舟擒钩|黑舸翻波</t>
+  </si>
+  <si>
+    <t>瞿娘</t>
+  </si>
+  <si>
+    <t>周旋</t>
+  </si>
+  <si>
+    <t>夺梢</t>
+  </si>
+  <si>
+    <t>招架</t>
+  </si>
+  <si>
+    <t>迅攻</t>
+  </si>
+  <si>
+    <t>佯攻</t>
+  </si>
+  <si>
+    <t>罴袭式</t>
+  </si>
+  <si>
+    <t>三段式</t>
+  </si>
+  <si>
+    <t>攻敌式</t>
+  </si>
+  <si>
+    <t>聚炁</t>
+  </si>
+  <si>
+    <t>试探试探</t>
+  </si>
+  <si>
+    <t>掷物</t>
+  </si>
+  <si>
+    <t>迎面对敌</t>
+  </si>
+  <si>
+    <t>倾力打击</t>
+  </si>
+  <si>
+    <t>通窍</t>
+  </si>
+  <si>
+    <t>祈咒</t>
+  </si>
+  <si>
+    <t>快服</t>
+  </si>
+  <si>
+    <t>基法</t>
+  </si>
+  <si>
+    <t>奇术</t>
+  </si>
+  <si>
+    <t>杀伐技</t>
+  </si>
+  <si>
+    <t>引炁为刃</t>
+  </si>
+  <si>
+    <t>汇点一破</t>
+  </si>
+  <si>
+    <t>绝玄戮命</t>
+  </si>
+  <si>
+    <t>启符</t>
   </si>
 </sst>
 </file>
@@ -1161,44 +1395,66 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1512,7 +1768,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W106"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2" customWidth="1"/>
@@ -1524,18 +1780,18 @@
     <col min="8" max="8" width="19.2222222222222" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.1111111111111" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.2222222222222" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.55555555555556" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.66666666666667" style="2" customWidth="1"/>
     <col min="12" max="12" width="14.2222222222222" style="2" customWidth="1"/>
     <col min="13" max="13" width="14.3333333333333" style="2" customWidth="1"/>
     <col min="14" max="14" width="7.33333333333333" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.55555555555556" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.6666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.3333333333333" style="2" customWidth="1"/>
-    <col min="18" max="20" width="13.2222222222222" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="17" max="20" width="13.3333333333333" style="2" customWidth="1"/>
+    <col min="21" max="23" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:23">
+    <row r="1" s="1" customFormat="1" ht="15.6" spans="1:26">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1559,137 +1815,152 @@
         <v>6</v>
       </c>
       <c r="I1" s="3"/>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="7"/>
+      <c r="N1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="7"/>
+      <c r="P1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="9" t="s">
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="7"/>
+      <c r="U1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="8"/>
-      <c r="W1" s="10"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:23">
+      <c r="V1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X1" s="7"/>
+      <c r="Z1" s="9"/>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="10"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="15.6" spans="1:23">
+      <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" s="9"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15.6" spans="1:26">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="K3" s="7"/>
       <c r="L3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="M3" s="7"/>
       <c r="N3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="O3" s="7"/>
       <c r="P3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" s="11"/>
-      <c r="U3" s="8"/>
-      <c r="W3" s="10"/>
-    </row>
-    <row r="4" ht="45" spans="1:18">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="8"/>
+      <c r="X3" s="7"/>
+      <c r="Z3" s="9"/>
+    </row>
+    <row r="4" ht="45" spans="1:21">
       <c r="A4" s="2">
         <v>800001</v>
       </c>
@@ -1697,259 +1968,259 @@
         <v>800001</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" ht="75" spans="1:18">
+        <v>38</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" ht="75" spans="1:21">
       <c r="A5" s="2">
         <v>800002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
         <v>800002</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" ht="45" spans="1:18">
+        <v>50</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" ht="45" spans="1:21">
       <c r="A6" s="2">
         <v>800003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2">
         <v>800003</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" ht="45" spans="1:18">
+        <v>55</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" ht="45" spans="1:21">
       <c r="A7" s="2">
         <v>800004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2">
         <v>800004</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" ht="45" spans="1:18">
+    </row>
+    <row r="8" ht="45" spans="1:21">
       <c r="A8" s="2">
         <v>800005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2">
         <v>800005</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" ht="45" spans="1:18">
+        <v>69</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" ht="45" spans="1:21">
       <c r="A9" s="2">
         <v>800006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2">
         <v>800006</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="P9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" ht="30" spans="1:18">
+      <c r="U9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="30" spans="1:21">
       <c r="A10" s="2">
         <v>800007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2">
         <v>800007</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:17">
@@ -1957,28 +2228,28 @@
         <v>800008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2">
         <v>800008</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1986,7 +2257,7 @@
         <v>800009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2">
         <v>800009</v>
@@ -2000,7 +2271,7 @@
         <v>800010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" s="2">
         <v>800010</v>
@@ -2014,7 +2285,7 @@
         <v>800011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2">
         <v>800011</v>
@@ -2028,7 +2299,7 @@
         <v>800012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2">
         <v>800012</v>
@@ -2042,7 +2313,7 @@
         <v>800013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D16" s="2">
         <v>800013</v>
@@ -2056,7 +2327,7 @@
         <v>800014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D17" s="2">
         <v>800014</v>
@@ -2070,7 +2341,7 @@
         <v>800015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2">
         <v>800015</v>
@@ -2084,7 +2355,7 @@
         <v>800016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D19" s="2">
         <v>800016</v>
@@ -2098,7 +2369,7 @@
         <v>800017</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2">
         <v>800017</v>
@@ -2112,7 +2383,7 @@
         <v>800018</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D21" s="2">
         <v>800018</v>
@@ -2126,7 +2397,7 @@
         <v>800019</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D22" s="2">
         <v>800019</v>
@@ -2140,7 +2411,7 @@
         <v>800020</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2">
         <v>800020</v>
@@ -2154,7 +2425,7 @@
         <v>800021</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D24" s="2">
         <v>800021</v>
@@ -2168,7 +2439,7 @@
         <v>800022</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" s="2">
         <v>800022</v>
@@ -2182,7 +2453,7 @@
         <v>800023</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D26" s="2">
         <v>800023</v>
@@ -2196,7 +2467,7 @@
         <v>800024</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D27" s="2">
         <v>800024</v>
@@ -2210,7 +2481,7 @@
         <v>800025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2">
         <v>800025</v>
@@ -2224,7 +2495,7 @@
         <v>800026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D29" s="2">
         <v>800026</v>
@@ -2238,7 +2509,7 @@
         <v>800027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D30" s="2">
         <v>800027</v>
@@ -2251,8 +2522,8 @@
       <c r="A31" s="2">
         <v>800028</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>91</v>
+      <c r="C31" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="D31" s="2">
         <v>800028</v>
@@ -2262,8 +2533,8 @@
       <c r="A32" s="2">
         <v>800029</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>92</v>
+      <c r="C32" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="D32" s="2">
         <v>800029</v>
@@ -2276,8 +2547,8 @@
       <c r="A33" s="2">
         <v>800030</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>92</v>
+      <c r="C33" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="D33" s="2">
         <v>800030</v>
@@ -2290,8 +2561,8 @@
       <c r="A34" s="2">
         <v>800031</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>92</v>
+      <c r="C34" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="D34" s="2">
         <v>800031</v>
@@ -2304,8 +2575,8 @@
       <c r="A35" s="2">
         <v>800032</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>93</v>
+      <c r="C35" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="D35" s="2">
         <v>800032</v>
@@ -2318,8 +2589,8 @@
       <c r="A36" s="2">
         <v>800033</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>93</v>
+      <c r="C36" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="D36" s="2">
         <v>800033</v>
@@ -2332,8 +2603,8 @@
       <c r="A37" s="2">
         <v>800034</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>93</v>
+      <c r="C37" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="D37" s="2">
         <v>800034</v>
@@ -2346,193 +2617,193 @@
       <c r="A38" s="2">
         <v>800035</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>94</v>
+      <c r="C38" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="D38" s="2">
         <v>800035</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="2">
         <v>800036</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>99</v>
+      <c r="C39" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="D39" s="2">
         <v>800036</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2">
         <v>800037</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>102</v>
+      <c r="C40" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D40" s="2">
         <v>800037</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="2">
         <v>800038</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>102</v>
+      <c r="C41" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D41" s="2">
         <v>800038</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2">
         <v>800039</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>102</v>
+      <c r="C42" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="D42" s="2">
         <v>800039</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2">
         <v>800040</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>103</v>
+      <c r="C43" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D43" s="2">
         <v>800040</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2">
         <v>800041</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>103</v>
+      <c r="C44" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D44" s="2">
         <v>800041</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2">
         <v>800042</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>103</v>
+      <c r="C45" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="D45" s="2">
         <v>800042</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2">
         <v>800043</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>104</v>
+      <c r="C46" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="D46" s="2">
         <v>800043</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2">
         <v>800044</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>104</v>
+      <c r="C47" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="D47" s="2">
         <v>800044</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2">
         <v>800045</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>104</v>
+      <c r="C48" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="D48" s="2">
         <v>800045</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2540,7 +2811,7 @@
         <v>800046</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D49" s="2">
         <v>800046</v>
@@ -2551,7 +2822,7 @@
         <v>800047</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D50" s="2">
         <v>800047</v>
@@ -2562,7 +2833,7 @@
         <v>800048</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D51" s="2">
         <v>800048</v>
@@ -2573,7 +2844,7 @@
         <v>800049</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D52" s="2">
         <v>800049</v>
@@ -2582,7 +2853,7 @@
         <v>10105</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2590,7 +2861,7 @@
         <v>800050</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D53" s="2">
         <v>800050</v>
@@ -2601,7 +2872,7 @@
         <v>800051</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D54" s="2">
         <v>800051</v>
@@ -2612,7 +2883,7 @@
         <v>800052</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D55" s="2">
         <v>800052</v>
@@ -2622,8 +2893,8 @@
       <c r="A56" s="2">
         <v>800053</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>108</v>
+      <c r="C56" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="D56" s="2">
         <v>800053</v>
@@ -2633,8 +2904,8 @@
       <c r="A57" s="2">
         <v>800054</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>108</v>
+      <c r="C57" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="D57" s="2">
         <v>800054</v>
@@ -2644,8 +2915,8 @@
       <c r="A58" s="2">
         <v>800055</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>108</v>
+      <c r="C58" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="D58" s="2">
         <v>800055</v>
@@ -2656,7 +2927,7 @@
         <v>800056</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D59" s="2">
         <v>800056</v>
@@ -2667,7 +2938,7 @@
         <v>800057</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D60" s="2">
         <v>800057</v>
@@ -2678,7 +2949,7 @@
         <v>800058</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D61" s="2">
         <v>800058</v>
@@ -2689,7 +2960,7 @@
         <v>800059</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D62" s="2">
         <v>800059</v>
@@ -2700,7 +2971,7 @@
         <v>800060</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D63" s="2">
         <v>800060</v>
@@ -2711,7 +2982,7 @@
         <v>800061</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D64" s="2">
         <v>800061</v>
@@ -2722,52 +2993,56 @@
         <v>800062</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D65" s="2">
         <v>800062</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:13">
       <c r="A66" s="2">
         <v>800063</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D66" s="2">
         <v>800063</v>
       </c>
+      <c r="J66" s="12"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="2">
         <v>800064</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D67" s="2">
         <v>800064</v>
       </c>
-      <c r="K67" s="6"/>
-      <c r="M67" s="6"/>
+      <c r="K67" s="1"/>
+      <c r="M67" s="1"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="2">
         <v>800065</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D68" s="2">
         <v>800065</v>
       </c>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6">
+      <c r="K68" s="1"/>
+      <c r="L68" s="1">
         <v>13058</v>
       </c>
-      <c r="M68" s="6" t="s">
-        <v>115</v>
+      <c r="M68" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -2775,16 +3050,16 @@
         <v>800066</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D69" s="2">
         <v>800066</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="1">
         <v>13059</v>
       </c>
-      <c r="M69" s="6" t="s">
-        <v>117</v>
+      <c r="M69" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2792,92 +3067,151 @@
         <v>800067</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D70" s="2">
         <v>800067</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="1">
         <v>13060</v>
       </c>
-      <c r="M70" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" ht="30" spans="1:15">
+      <c r="M70" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" ht="30" spans="1:24">
       <c r="A71" s="2">
         <v>800068</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D71" s="2">
         <v>800068</v>
       </c>
-      <c r="H71" s="6">
-        <v>10116</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>121</v>
+      <c r="H71" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K71" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="L71" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="M71" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="N71" s="6">
+        <v>126</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N71" s="1">
         <v>14040</v>
       </c>
-      <c r="O71" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="O71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="X71" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" ht="30" spans="1:24">
       <c r="A72" s="2">
         <v>800069</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D72" s="2">
         <v>800069</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="H72" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N72" s="1">
+        <v>14040</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="X72" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="73" ht="30" spans="1:24">
       <c r="A73" s="2">
         <v>800070</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D73" s="2">
         <v>800070</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="H73" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N73" s="1">
+        <v>14040</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="2">
         <v>800071</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D74" s="2">
         <v>800071</v>
       </c>
+      <c r="M74" s="12"/>
+      <c r="N74" s="15"/>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
         <v>800072</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D75" s="2">
         <v>800072</v>
@@ -2888,7 +3222,7 @@
         <v>800073</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D76" s="2">
         <v>800073</v>
@@ -2899,7 +3233,7 @@
         <v>800074</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D77" s="2">
         <v>800074</v>
@@ -2910,34 +3244,34 @@
         <v>800075</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D78" s="2">
         <v>800075</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N78" s="2">
         <v>14062</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" ht="45" spans="1:15">
@@ -2945,34 +3279,34 @@
         <v>800076</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D79" s="2">
         <v>800076</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N79" s="2">
         <v>14070</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" ht="60" spans="1:15">
@@ -2980,34 +3314,34 @@
         <v>800077</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D80" s="2">
         <v>800077</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="N80" s="6">
+        <v>145</v>
+      </c>
+      <c r="N80" s="1">
         <v>14071</v>
       </c>
-      <c r="O80" s="6" t="s">
-        <v>135</v>
+      <c r="O80" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="81" ht="45" spans="1:17">
@@ -3015,40 +3349,40 @@
         <v>800078</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D81" s="2">
         <v>800078</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L81" s="12" t="s">
-        <v>150</v>
+        <v>160</v>
+      </c>
+      <c r="L81" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" ht="45" spans="1:17">
@@ -3056,40 +3390,40 @@
         <v>800079</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D82" s="2">
         <v>800079</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L82" s="12" t="s">
-        <v>150</v>
+        <v>160</v>
+      </c>
+      <c r="L82" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" ht="45" spans="1:17">
@@ -3097,40 +3431,40 @@
         <v>800080</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D83" s="2">
         <v>800080</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L83" s="12" t="s">
-        <v>150</v>
+        <v>160</v>
+      </c>
+      <c r="L83" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" spans="1:15">
@@ -3138,7 +3472,7 @@
         <v>800081</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D84" s="2">
         <v>800081</v>
@@ -3146,171 +3480,571 @@
       <c r="H84" s="2">
         <v>10136</v>
       </c>
-      <c r="I84" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="N84" s="6">
+      <c r="I84" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="N84" s="1">
         <v>14065</v>
       </c>
-      <c r="O84" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="O84" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" ht="45" spans="1:15">
       <c r="A85" s="2">
         <v>800082</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>159</v>
+      <c r="C85" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D85" s="2">
         <v>800082</v>
       </c>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-    </row>
-    <row r="86" spans="1:18">
+      <c r="H85" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="O85" s="1"/>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" s="2">
         <v>800083</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D86" s="2">
         <v>800083</v>
       </c>
-      <c r="N86" s="6"/>
-      <c r="O86" s="6"/>
-      <c r="R86" s="2">
+      <c r="H86" s="10"/>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="U86" s="2">
         <v>800083</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:21">
       <c r="A87" s="2">
         <v>800084</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D87" s="2">
         <v>800084</v>
       </c>
-      <c r="N87" s="6"/>
-      <c r="O87" s="6"/>
-      <c r="R87" s="2">
+      <c r="H87" s="10"/>
+      <c r="I87" s="16"/>
+      <c r="J87" s="16"/>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
+      <c r="U87" s="2">
         <v>800084</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:21">
       <c r="A88" s="2">
         <v>800085</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D88" s="2">
         <v>800085</v>
       </c>
-      <c r="N88" s="6"/>
-      <c r="O88" s="6"/>
-      <c r="R88" s="2">
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="U88" s="2">
         <v>800085</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" ht="45" spans="1:13">
       <c r="A89" s="2">
         <v>800086</v>
       </c>
-      <c r="N89" s="6"/>
-      <c r="O89" s="6"/>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="C89" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D89" s="2">
+        <v>800086</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K89" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="90" ht="45" spans="1:13">
       <c r="A90" s="2">
         <v>800087</v>
       </c>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-    </row>
-    <row r="91" spans="1:15">
+      <c r="C90" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" s="2">
+        <v>800087</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K90" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" ht="60" spans="1:13">
       <c r="A91" s="2">
         <v>800088</v>
       </c>
-      <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-    </row>
-    <row r="92" spans="1:1">
+      <c r="C91" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="2">
+        <v>800088</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K91" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="92" ht="45" spans="1:15">
       <c r="A92" s="2">
         <v>800089</v>
       </c>
-    </row>
-    <row r="93" spans="1:1">
+      <c r="C92" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="2">
+        <v>800089</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="N92" s="2">
+        <v>14040</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="93" ht="45" spans="1:13">
       <c r="A93" s="2">
         <v>800090</v>
       </c>
-    </row>
-    <row r="94" spans="1:1">
+      <c r="C93" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D93" s="2">
+        <v>800090</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K93" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="94" ht="60" spans="1:13">
       <c r="A94" s="2">
         <v>800091</v>
       </c>
-    </row>
-    <row r="95" spans="1:1">
+      <c r="C94" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D94" s="2">
+        <v>800091</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K94" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="95" ht="30" spans="1:15">
       <c r="A95" s="2">
         <v>800092</v>
       </c>
-    </row>
-    <row r="96" spans="1:1">
+      <c r="C95" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D95" s="2">
+        <v>800092</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K95" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N95" s="2">
+        <v>14040</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" s="2">
         <v>800093</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="C96" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D96" s="2">
+        <v>800093</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
       <c r="A97" s="2">
         <v>800094</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="18"/>
+      <c r="S97" s="12"/>
+      <c r="T97" s="15"/>
+    </row>
+    <row r="98" spans="1:20">
       <c r="A98" s="2">
         <v>800095</v>
       </c>
-    </row>
-    <row r="99" spans="1:1">
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="S98" s="12"/>
+      <c r="T98" s="15"/>
+    </row>
+    <row r="99" spans="1:20">
       <c r="A99" s="2">
         <v>800096</v>
       </c>
-    </row>
-    <row r="100" spans="1:1">
+      <c r="S99" s="12"/>
+      <c r="T99" s="15"/>
+    </row>
+    <row r="100" spans="1:20">
       <c r="A100" s="2">
         <v>800097</v>
       </c>
-    </row>
-    <row r="101" spans="1:1">
+      <c r="Q100" s="12"/>
+      <c r="R100" s="15"/>
+      <c r="S100" s="12"/>
+      <c r="T100" s="15"/>
+    </row>
+    <row r="101" spans="1:20">
       <c r="A101" s="2">
         <v>800098</v>
       </c>
-    </row>
-    <row r="102" spans="1:1">
+      <c r="M101" s="12">
+        <v>11029</v>
+      </c>
+      <c r="N101" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="R101" s="17"/>
+      <c r="S101" s="12"/>
+      <c r="T101" s="15"/>
+    </row>
+    <row r="102" spans="1:20">
       <c r="A102" s="2">
         <v>800099</v>
       </c>
-    </row>
-    <row r="103" spans="1:1">
+      <c r="M102" s="12">
+        <v>13053</v>
+      </c>
+      <c r="N102" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="R102" s="17"/>
+      <c r="S102" s="12"/>
+      <c r="T102" s="15"/>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" s="2">
         <v>800100</v>
       </c>
-    </row>
-    <row r="104" spans="1:1">
+      <c r="M103" s="12">
+        <v>11005</v>
+      </c>
+      <c r="N103" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="P103" s="17"/>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" s="2">
         <v>800101</v>
       </c>
-    </row>
-    <row r="105" spans="1:1">
+      <c r="M104" s="12">
+        <v>13007</v>
+      </c>
+      <c r="N104" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="O104" s="12">
+        <v>13001</v>
+      </c>
+      <c r="P104" s="15" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" s="2">
         <v>800102</v>
       </c>
-    </row>
-    <row r="106" spans="1:1">
+      <c r="M105" s="12">
+        <v>13063</v>
+      </c>
+      <c r="N105" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="O105" s="12">
+        <v>13002</v>
+      </c>
+      <c r="P105" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" s="2">
         <v>800103</v>
+      </c>
+      <c r="M106" s="12">
+        <v>11005</v>
+      </c>
+      <c r="N106" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="O106" s="12">
+        <v>13003</v>
+      </c>
+      <c r="P106" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="107" spans="13:16">
+      <c r="M107" s="12">
+        <v>11009</v>
+      </c>
+      <c r="N107" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="O107" s="12">
+        <v>13004</v>
+      </c>
+      <c r="P107" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="13:16">
+      <c r="M108" s="12">
+        <v>13016</v>
+      </c>
+      <c r="N108" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="O108" s="12">
+        <v>13005</v>
+      </c>
+      <c r="P108" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="109" spans="15:16">
+      <c r="O109" s="12">
+        <v>13006</v>
+      </c>
+      <c r="P109" s="15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="112" spans="13:14">
+      <c r="M112" s="12">
+        <v>14042</v>
+      </c>
+      <c r="N112" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="113" spans="13:14">
+      <c r="M113" s="12">
+        <v>14044</v>
+      </c>
+      <c r="N113" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="114" spans="13:14">
+      <c r="M114" s="12">
+        <v>11009</v>
+      </c>
+      <c r="N114" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="13:14">
+      <c r="M115" s="15">
+        <v>11013</v>
+      </c>
+      <c r="N115" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="116" spans="13:14">
+      <c r="M116" s="15">
+        <v>12001</v>
+      </c>
+      <c r="N116" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="13:14">
+      <c r="M117" s="15">
+        <v>12002</v>
+      </c>
+      <c r="N117" s="15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="13:14">
+      <c r="M118" s="15">
+        <v>12003</v>
+      </c>
+      <c r="N118" s="15" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="13:14">
+      <c r="M119" s="15">
+        <v>12004</v>
+      </c>
+      <c r="N119" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="120" spans="13:14">
+      <c r="M120" s="15">
+        <v>12005</v>
+      </c>
+      <c r="N120" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="13:14">
+      <c r="M121" s="15">
+        <v>12006</v>
+      </c>
+      <c r="N121" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="13:14">
+      <c r="M122" s="12">
+        <v>14018</v>
+      </c>
+      <c r="N122" s="15" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
